--- a/xls/square_20_tri3_22.xlsx
+++ b/xls/square_20_tri3_22.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>529</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>441</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>2.62535068139611</v>
+      </c>
+      <c r="J20">
+        <v>-0.9199990661520724</v>
+      </c>
+      <c r="K20">
+        <v>0.6774283811192275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>529</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>441</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>0.4476971916532505</v>
+      </c>
+      <c r="J21">
+        <v>-2.0940890292225403</v>
+      </c>
+      <c r="K21">
+        <v>1.254931868766168</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
